--- a/VehicleParameters.xlsx
+++ b/VehicleParameters.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,13 +10,13 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6FEEB4-F76C-4658-923E-5D3996E0B5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="MuTable" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="183" uniqueCount="122">
   <si>
     <t>Name</t>
   </si>
@@ -331,13 +331,82 @@
   </si>
   <si>
     <t>Empirical thermal derating, "fudge factor"</t>
+  </si>
+  <si>
+    <t>current_limit_actual</t>
+  </si>
+  <si>
+    <t>torque_limit_total_MN</t>
+  </si>
+  <si>
+    <t>regen_power_limit</t>
+  </si>
+  <si>
+    <t>regen_max_curve_a</t>
+  </si>
+  <si>
+    <t>regen_max_curve_b</t>
+  </si>
+  <si>
+    <t>regen_efficiency</t>
+  </si>
+  <si>
+    <t>min_regen_speed</t>
+  </si>
+  <si>
+    <t>min_energy_threshold</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>%Mn</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Nm</t>
+  </si>
+  <si>
+    <t>mph</t>
+  </si>
+  <si>
+    <t>kJ</t>
+  </si>
+  <si>
+    <t>vehicle setting</t>
+  </si>
+  <si>
+    <t>Motor controller current limit the loaded data was recorded at. Predicted-regen curves scale by current_limit/current_limit_actual.</t>
+  </si>
+  <si>
+    <t>Maximum observed total motor torque command, all 4 wheels combined. Wheel-side limit = value/100*9.8*gear_ratio.</t>
+  </si>
+  <si>
+    <t>Motor controller regen power limit.</t>
+  </si>
+  <si>
+    <t>Max regen wheel torque curve: T = a*mph^b, before efficiency and current-limit scaling.</t>
+  </si>
+  <si>
+    <t>Exponent of the max regen wheel torque curve (negative: available torque falls with speed).</t>
+  </si>
+  <si>
+    <t>Utilization factor applied to the theoretical max regen curve to match measured data.</t>
+  </si>
+  <si>
+    <t>Minimum vehicle speed for regen; below this the system recovers no energy.</t>
+  </si>
+  <si>
+    <t>Minimum cumulative regen energy before the predicted-vs-actual percent difference is reported (avoids a near-zero denominator early in a run).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -356,7 +425,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -364,13 +433,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,7 +460,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -540,7 +611,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -564,9 +635,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -590,7 +661,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -625,7 +696,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -643,7 +714,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -668,7 +739,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -704,18 +775,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.3046875" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="9.765625" customWidth="1"/>
-    <col min="4" max="4" width="17.61328125" customWidth="1"/>
-    <col min="5" max="5" width="120.69140625" customWidth="1"/>
+    <col min="1" max="1" width="21.3046875" customWidth="true"/>
+    <col min="2" max="2" width="10" customWidth="true"/>
+    <col min="3" max="3" width="9.765625" customWidth="true"/>
+    <col min="4" max="4" width="17.61328125" customWidth="true"/>
+    <col min="5" max="5" width="120.69140625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -732,7 +803,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -749,7 +820,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -766,7 +837,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -783,7 +854,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -800,7 +871,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -817,7 +888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -834,7 +905,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -851,7 +922,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -868,7 +939,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -885,7 +956,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -902,7 +973,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -916,7 +987,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -933,7 +1004,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -950,7 +1021,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -967,7 +1038,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -984,7 +1055,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1001,7 +1072,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1018,7 +1089,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1035,7 +1106,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1052,7 +1123,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1069,7 +1140,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1086,7 +1157,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1103,7 +1174,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1120,7 +1191,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1137,7 +1208,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1154,7 +1225,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1168,7 +1239,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1182,7 +1253,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1199,7 +1270,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1213,7 +1284,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1227,7 +1298,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1244,7 +1315,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1258,7 +1329,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1275,7 +1346,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1289,7 +1360,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1306,7 +1377,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1320,7 +1391,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1337,7 +1408,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1352,6 +1423,142 @@
       </c>
       <c r="E39" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="0">
+        <v>35</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="0">
+        <v>200</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="0">
+        <v>30000</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="0">
+        <v>7041</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" s="0">
+        <v>-0.93500000000000005</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="0">
+        <v>0.66000000000000003</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="0">
+        <v>5</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="0">
+        <v>50</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
